--- a/Result/profitability/2702.xlsx
+++ b/Result/profitability/2702.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.09</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04125000000000002</v>
+        <v>-0.002500000000000016</v>
       </c>
       <c r="N2" t="n">
-        <v>86.34375</v>
+        <v>86.44625000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.08</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.007500000000000015</v>
+        <v>0.01624999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>85.57375</v>
+        <v>85.8425</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.001250000000000015</v>
+        <v>-0.01250000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>84.80625000000001</v>
+        <v>85.175</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003749999999999986</v>
+        <v>0.15125</v>
       </c>
       <c r="N5" t="n">
-        <v>83.9225</v>
+        <v>84.20375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>0.16</v>
+        <v>0.145</v>
       </c>
       <c r="N6" t="n">
-        <v>82.80249999999999</v>
+        <v>83.12875000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.37</v>
       </c>
       <c r="M7" t="n">
-        <v>0.17625</v>
+        <v>0.15875</v>
       </c>
       <c r="N7" t="n">
-        <v>82.26625</v>
+        <v>82.22375000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.11</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1575</v>
+        <v>0.14875</v>
       </c>
       <c r="N8" t="n">
-        <v>81.25375</v>
+        <v>81.19625000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0.1975</v>
       </c>
       <c r="N11" t="n">
-        <v>79.81999999999999</v>
+        <v>79.82000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.2275</v>
       </c>
       <c r="N12" t="n">
-        <v>79.97999999999999</v>
+        <v>79.98</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>375</v>
+      </c>
+      <c r="D75" t="n">
+        <v>42</v>
+      </c>
+      <c r="E75" t="n">
+        <v>334</v>
+      </c>
+      <c r="F75" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>41</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.05%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-25</v>
+      </c>
+      <c r="J75" t="n">
+        <v>16</v>
+      </c>
+      <c r="K75" t="n">
+        <v>18</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.03750000000000002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>87.65249999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.368421052631579</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.4599999999999937</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.005147717099373228</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.113207547169811</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.02596653202538945</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
